--- a/templates/Tuck Shops.template.xlsx
+++ b/templates/Tuck Shops.template.xlsx
@@ -429,13 +429,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,6 +462,21 @@
           <t>Hours</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delivery (Rs)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Payment note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -477,6 +495,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>mohanda@okaxis</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -489,8 +514,21 @@
           <t>Tagore Tuck Shop</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>7602416780</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>shop@ybl</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
